--- a/SensitivityAnalysis/SingleSNP/MR_res_binarySA.xlsx
+++ b/SensitivityAnalysis/SingleSNP/MR_res_binarySA.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="18">
   <si>
     <t>id.exposure</t>
   </si>
@@ -44,15 +44,6 @@
   </si>
   <si>
     <t>pval</t>
-  </si>
-  <si>
-    <t>OR</t>
-  </si>
-  <si>
-    <t>C1_L</t>
-  </si>
-  <si>
-    <t>C2_U</t>
   </si>
   <si>
     <t>1</t>
@@ -156,34 +147,25 @@
       <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" t="s">
-        <v>9</v>
-      </c>
-      <c r="L1" t="s">
-        <v>10</v>
-      </c>
-      <c r="M1" t="s">
-        <v>11</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" t="s">
         <v>12</v>
-      </c>
-      <c r="B2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" t="s">
-        <v>15</v>
       </c>
       <c r="G2" t="n">
         <v>1.0</v>
@@ -196,15 +178,6 @@
       </c>
       <c r="J2" t="n">
         <v>6.164740300279638E-7</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0.14916487749798976</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0.07060464420633376</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0.3151373529192614</v>
       </c>
     </row>
   </sheetData>
@@ -246,34 +219,25 @@
       <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" t="s">
-        <v>9</v>
-      </c>
-      <c r="L1" t="s">
-        <v>10</v>
-      </c>
-      <c r="M1" t="s">
-        <v>11</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" t="s">
         <v>12</v>
-      </c>
-      <c r="B2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" t="s">
-        <v>15</v>
       </c>
       <c r="G2" t="n">
         <v>1.0</v>
@@ -286,15 +250,6 @@
       </c>
       <c r="J2" t="n">
         <v>0.19446273141300288</v>
-      </c>
-      <c r="K2" t="n">
-        <v>1.669147336396878</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0.7698252705085403</v>
-      </c>
-      <c r="M2" t="n">
-        <v>3.6190716742259563</v>
       </c>
     </row>
   </sheetData>
@@ -336,34 +291,25 @@
       <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" t="s">
-        <v>9</v>
-      </c>
-      <c r="L1" t="s">
-        <v>10</v>
-      </c>
-      <c r="M1" t="s">
-        <v>11</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" t="s">
         <v>12</v>
-      </c>
-      <c r="B2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" t="s">
-        <v>15</v>
       </c>
       <c r="G2" t="n">
         <v>1.0</v>
@@ -376,15 +322,6 @@
       </c>
       <c r="J2" t="n">
         <v>0.23783435139778353</v>
-      </c>
-      <c r="K2" t="n">
-        <v>1.7934167918654214</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0.6799254667627381</v>
-      </c>
-      <c r="M2" t="n">
-        <v>4.730435829471898</v>
       </c>
     </row>
   </sheetData>
@@ -426,34 +363,25 @@
       <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" t="s">
-        <v>9</v>
-      </c>
-      <c r="L1" t="s">
-        <v>10</v>
-      </c>
-      <c r="M1" t="s">
-        <v>11</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" t="s">
         <v>12</v>
-      </c>
-      <c r="B2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" t="s">
-        <v>15</v>
       </c>
       <c r="G2" t="n">
         <v>1.0</v>
@@ -466,15 +394,6 @@
       </c>
       <c r="J2" t="n">
         <v>0.9748855927589639</v>
-      </c>
-      <c r="K2" t="n">
-        <v>1.0248079559359686</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0.2228706261944387</v>
-      </c>
-      <c r="M2" t="n">
-        <v>4.7122914512449325</v>
       </c>
     </row>
   </sheetData>
@@ -516,34 +435,25 @@
       <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" t="s">
-        <v>9</v>
-      </c>
-      <c r="L1" t="s">
-        <v>10</v>
-      </c>
-      <c r="M1" t="s">
-        <v>11</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" t="s">
         <v>12</v>
-      </c>
-      <c r="B2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" t="s">
-        <v>15</v>
       </c>
       <c r="G2" t="n">
         <v>1.0</v>
@@ -556,15 +466,6 @@
       </c>
       <c r="J2" t="n">
         <v>0.4667622585995815</v>
-      </c>
-      <c r="K2" t="n">
-        <v>1.1403554894964651</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0.800606456016507</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1.6242819835541153</v>
       </c>
     </row>
   </sheetData>
@@ -606,34 +507,25 @@
       <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" t="s">
-        <v>9</v>
-      </c>
-      <c r="L1" t="s">
-        <v>10</v>
-      </c>
-      <c r="M1" t="s">
-        <v>11</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" t="s">
         <v>12</v>
-      </c>
-      <c r="B2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" t="s">
-        <v>15</v>
       </c>
       <c r="G2" t="n">
         <v>1.0</v>
@@ -646,15 +538,6 @@
       </c>
       <c r="J2" t="n">
         <v>0.034475735526612504</v>
-      </c>
-      <c r="K2" t="n">
-        <v>2.710233602604278</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1.0755521128219176</v>
-      </c>
-      <c r="M2" t="n">
-        <v>6.8293912429899715</v>
       </c>
     </row>
   </sheetData>

--- a/SensitivityAnalysis/SingleSNP/MR_res_binarySA.xlsx
+++ b/SensitivityAnalysis/SingleSNP/MR_res_binarySA.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="21">
   <si>
     <t>id.exposure</t>
   </si>
@@ -44,6 +44,15 @@
   </si>
   <si>
     <t>pval</t>
+  </si>
+  <si>
+    <t>OR</t>
+  </si>
+  <si>
+    <t>CI_LOW_OR</t>
+  </si>
+  <si>
+    <t>CI_HIGH_OR</t>
   </si>
   <si>
     <t>1</t>
@@ -147,37 +156,55 @@
       <c r="J1" t="s">
         <v>8</v>
       </c>
+      <c r="K1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G2" t="n">
         <v>1.0</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.9027030244341547</v>
+        <v>4.498214413023184</v>
       </c>
       <c r="I2" t="n">
-        <v>0.38161037257802166</v>
+        <v>1.2933171079408585</v>
       </c>
       <c r="J2" t="n">
-        <v>6.164740300279638E-7</v>
+        <v>5.050861259054412E-4</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.011128850337854481</v>
+      </c>
+      <c r="L2" t="n">
+        <v>8.821786736957576E-4</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.14039254579064697</v>
       </c>
     </row>
   </sheetData>
@@ -219,37 +246,55 @@
       <c r="J1" t="s">
         <v>8</v>
       </c>
+      <c r="K1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G2" t="n">
         <v>1.0</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5123129190319816</v>
+        <v>-0.7805343865898409</v>
       </c>
       <c r="I2" t="n">
-        <v>0.39484930119103556</v>
+        <v>0.5502609083604812</v>
       </c>
       <c r="J2" t="n">
-        <v>0.19446273141300288</v>
+        <v>0.15605051823214933</v>
+      </c>
+      <c r="K2" t="n">
+        <v>2.1826383265589406</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.7423184174797509</v>
+      </c>
+      <c r="M2" t="n">
+        <v>6.4176099533377995</v>
       </c>
     </row>
   </sheetData>
@@ -291,37 +336,55 @@
       <c r="J1" t="s">
         <v>8</v>
       </c>
+      <c r="K1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G2" t="n">
         <v>1.0</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5841226226376333</v>
+        <v>-1.039065936179388</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4948442434483861</v>
+        <v>0.8344705417185669</v>
       </c>
       <c r="J2" t="n">
-        <v>0.23783435139778353</v>
+        <v>0.2130656334964451</v>
+      </c>
+      <c r="K2" t="n">
+        <v>2.826575578924476</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.5507378658503298</v>
+      </c>
+      <c r="M2" t="n">
+        <v>14.50695512108386</v>
       </c>
     </row>
   </sheetData>
@@ -363,37 +426,55 @@
       <c r="J1" t="s">
         <v>8</v>
       </c>
+      <c r="K1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" t="s">
         <v>15</v>
-      </c>
-      <c r="D2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" t="s">
-        <v>12</v>
       </c>
       <c r="G2" t="n">
         <v>1.0</v>
       </c>
       <c r="H2" t="n">
-        <v>0.024505234973812805</v>
+        <v>0.5356770820750164</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7784025828792497</v>
+        <v>0.9923836439616037</v>
       </c>
       <c r="J2" t="n">
-        <v>0.9748855927589639</v>
+        <v>0.5893430353599407</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.5852728781834101</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.08368052337198466</v>
+      </c>
+      <c r="M2" t="n">
+        <v>4.093477527792004</v>
       </c>
     </row>
   </sheetData>
@@ -435,37 +516,55 @@
       <c r="J1" t="s">
         <v>8</v>
       </c>
+      <c r="K1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G2" t="n">
         <v>1.0</v>
       </c>
       <c r="H2" t="n">
-        <v>0.13134004668826924</v>
+        <v>-0.29909621312152723</v>
       </c>
       <c r="I2" t="n">
-        <v>0.18047235467948594</v>
+        <v>0.3763271579527086</v>
       </c>
       <c r="J2" t="n">
-        <v>0.4667622585995815</v>
+        <v>0.4267431650463671</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1.3486393740349476</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.644999964989777</v>
+      </c>
+      <c r="M2" t="n">
+        <v>2.8198887750733497</v>
       </c>
     </row>
   </sheetData>
@@ -507,37 +606,55 @@
       <c r="J1" t="s">
         <v>8</v>
       </c>
+      <c r="K1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G2" t="n">
         <v>1.0</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9970348313995647</v>
+        <v>-0.859466204118709</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4715309736434358</v>
+        <v>0.685326684037511</v>
       </c>
       <c r="J2" t="n">
-        <v>0.034475735526612504</v>
+        <v>0.20980671585189617</v>
+      </c>
+      <c r="K2" t="n">
+        <v>2.36189958487796</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.616452444890403</v>
+      </c>
+      <c r="M2" t="n">
+        <v>9.049472826794407</v>
       </c>
     </row>
   </sheetData>
